--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.13618866625129</v>
+        <v>4.247130658265835</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9748494008607</v>
+        <v>4.383413027639865</v>
       </c>
       <c r="E2" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F2" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.6298047246019</v>
+        <v>3.352343267747808</v>
       </c>
       <c r="D3" t="n">
-        <v>21.42715680319027</v>
+        <v>3.481912980518419</v>
       </c>
       <c r="E3" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F3" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.96855153279217</v>
+        <v>4.057389624078728</v>
       </c>
       <c r="D4" t="n">
-        <v>6.191832545342248</v>
+        <v>1.006172788618115</v>
       </c>
       <c r="E4" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F4" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.595995738745843</v>
+        <v>1.3968493075462</v>
       </c>
       <c r="D5" t="n">
-        <v>14.0089257261219</v>
+        <v>2.276450430494809</v>
       </c>
       <c r="E5" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F5" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.47768114165304</v>
+        <v>4.465123185518618</v>
       </c>
       <c r="D6" t="n">
-        <v>9.300537618869138</v>
+        <v>1.511337363066235</v>
       </c>
       <c r="E6" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F6" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.78253181451069</v>
+        <v>3.864661419857988</v>
       </c>
       <c r="D7" t="n">
-        <v>12.5099960031968</v>
+        <v>2.032874350519481</v>
       </c>
       <c r="E7" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F7" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.58440800380673</v>
+        <v>3.182466300618593</v>
       </c>
       <c r="D8" t="n">
-        <v>4.248710512302576</v>
+        <v>0.6904154582491687</v>
       </c>
       <c r="E8" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F8" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>15.75363765920292</v>
+        <v>2.559966119620474</v>
       </c>
       <c r="D9" t="n">
-        <v>14.53335442238971</v>
+        <v>2.361670093638327</v>
       </c>
       <c r="E9" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F9" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61068267929694</v>
+        <v>4.649235935385754</v>
       </c>
       <c r="D10" t="n">
-        <v>20.94172671404065</v>
+        <v>3.403030591031605</v>
       </c>
       <c r="E10" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F10" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>9.830179356122906</v>
+        <v>1.597404145369972</v>
       </c>
       <c r="D11" t="n">
-        <v>4.843622159458697</v>
+        <v>0.7870886009120382</v>
       </c>
       <c r="E11" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F11" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.80439653090716</v>
+        <v>6.468214436272413</v>
       </c>
       <c r="D12" t="n">
-        <v>7.927422901060123</v>
+        <v>1.28820622142227</v>
       </c>
       <c r="E12" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F12" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.87712914179609</v>
+        <v>8.105033485541865</v>
       </c>
       <c r="D13" t="n">
-        <v>18.07340793706384</v>
+        <v>2.936928789772875</v>
       </c>
       <c r="E13" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F13" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.35062685925099</v>
+        <v>2.656976864628287</v>
       </c>
       <c r="D14" t="n">
-        <v>18.25195417033178</v>
+        <v>2.965942552678915</v>
       </c>
       <c r="E14" t="n">
-        <v>10.93236837992089</v>
+        <v>1.776509861737145</v>
       </c>
       <c r="F14" t="n">
-        <v>6.833965828383276</v>
+        <v>1.110519447112282</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
